--- a/output/pdf_financials_xlsx/ZOMD.xlsx
+++ b/output/pdf_financials_xlsx/ZOMD.xlsx
@@ -697,10 +697,10 @@
         <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>0.082369</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>0.039942</v>
       </c>
       <c r="F10" s="1" t="inlineStr">
         <is>
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>0</v>
+        <v>-0.082369</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>0</v>
+        <v>-0.039942</v>
       </c>
       <c r="F11" s="1" t="inlineStr">
         <is>
@@ -1437,22 +1437,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0815</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.254582</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.163643</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.130796</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.11334</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.049744</v>
       </c>
     </row>
     <row r="35">
@@ -1487,22 +1487,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0815</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.254582</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.163643</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.130796</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.11334</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.049744</v>
       </c>
     </row>
     <row r="37">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E11" s="5" t="n">
@@ -7358,11 +7358,7 @@
           <t>General and administrative fees</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -7496,7 +7492,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">

--- a/output/pdf_financials_xlsx/ZOMD.xlsx
+++ b/output/pdf_financials_xlsx/ZOMD.xlsx
@@ -514,15 +514,11 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -545,15 +541,11 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -578,15 +570,11 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -609,15 +597,11 @@
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -640,15 +624,11 @@
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -671,15 +651,11 @@
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -702,15 +678,11 @@
       <c r="E10" s="3" t="n">
         <v>0.039942</v>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="3" t="n">
+        <v>0.080455</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.06651700000000001</v>
       </c>
     </row>
     <row r="11">
@@ -735,15 +707,11 @@
       <c r="E11" s="3" t="n">
         <v>-0.039942</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="3" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>-0.06651700000000001</v>
       </c>
     </row>
     <row r="12">
@@ -766,15 +734,11 @@
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -797,15 +761,11 @@
       <c r="E13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -828,15 +788,11 @@
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -859,15 +815,11 @@
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -890,15 +842,11 @@
       <c r="E16" s="3" t="n">
         <v>-0.039942</v>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="3" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>-0.06651700000000001</v>
       </c>
     </row>
     <row r="17">
@@ -921,15 +869,11 @@
       <c r="E17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1026,15 +970,11 @@
       <c r="E20" s="3" t="n">
         <v>-0.039942</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>-0.06651700000000001</v>
       </c>
     </row>
     <row r="21">
@@ -1057,15 +997,11 @@
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1088,15 +1024,11 @@
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1119,15 +1051,11 @@
       <c r="E23" s="3" t="n">
         <v>-0.039942</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>-0.06651700000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1148,17 +1076,13 @@
         <v>-0.02</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.04</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="25">
@@ -1179,17 +1103,13 @@
         <v>-0.02</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.04</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>-0.05</v>
       </c>
     </row>
     <row r="26">
@@ -1211,20 +1131,14 @@
       <c r="D26" s="3" t="n">
         <v>4.11845</v>
       </c>
-      <c r="E26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E26" s="3" t="n">
+        <v>0.99855</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1.149357</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1.33034</v>
       </c>
     </row>
     <row r="27">
@@ -1247,15 +1161,11 @@
       <c r="E27" s="3" t="n">
         <v>-0.039942</v>
       </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="3" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>-0.06651700000000001</v>
       </c>
     </row>
     <row r="28">
@@ -1276,15 +1186,11 @@
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1307,15 +1213,11 @@
       <c r="E29" s="3" t="n">
         <v>-0.039942</v>
       </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="3" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>-0.06651700000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1375,15 +1277,11 @@
       <c r="E31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3123,10 +3021,8 @@
       <c r="E99" s="3" t="n">
         <v>-0.039942</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>-0.080455</v>
       </c>
       <c r="G99" s="1" t="inlineStr">
         <is>
@@ -4147,7 +4043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -7355,10 +7251,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>General and administrative fees</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>General and administrative (note 5)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>-</t>
@@ -7369,21 +7269,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G68" s="5" t="n">
-        <v>0.003459</v>
-      </c>
-      <c r="H68" s="5" t="n">
-        <v>-0.000172</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>0.015969</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>0.031758</v>
       </c>
     </row>
     <row r="69">
@@ -7399,7 +7299,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Professional fees (note 5)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -7412,24 +7312,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>0.02655</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>0.059351</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H69" s="5" t="n">
         <v>0.01966</v>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I69" s="5" t="n">
+        <v>0.041339</v>
+      </c>
+      <c r="J69" s="5" t="n">
+        <v>0.01189</v>
       </c>
     </row>
     <row r="70">
@@ -7463,15 +7363,11 @@
       <c r="H70" s="5" t="n">
         <v>0.020454</v>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I70" s="5" t="n">
+        <v>0.023147</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>0.015245</v>
       </c>
     </row>
     <row r="71">
@@ -7487,14 +7383,10 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Transaction costs (note 6)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
@@ -7505,21 +7397,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G71" s="5" t="n">
-        <v>0.082369</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>0.039942</v>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J71" s="5" t="n">
+        <v>0.007624</v>
       </c>
     </row>
     <row r="72">
@@ -7535,12 +7429,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss $</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7548,24 +7442,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.046276</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>-0.082369</v>
+        <v>0.082369</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>-0.039942</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.039942</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>0.080455</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>0.06651700000000001</v>
       </c>
     </row>
     <row r="73">
@@ -7576,17 +7468,17 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Loss and comprehensive per share</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Basic and diluted</t>
+          <t>Net Loss and Comprehensive Loss for the Year</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7599,21 +7491,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="H73" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-0.06651700000000001</v>
       </c>
     </row>
     <row r="74">
@@ -7622,15 +7514,19 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Revenue $</t>
+          <t>Basic and Diluted Loss Per Common Share</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>TotalRevenue</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7653,15 +7549,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I74" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>-5e-08</v>
       </c>
     </row>
     <row r="75">
@@ -7672,42 +7564,42 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Weighted Average Number of Common Shares</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Share-based compensation</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>Weighted Average Number of Common Shares total</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>0.003057</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H75" s="5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>1.223288</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>1.31</v>
       </c>
     </row>
     <row r="76">
@@ -7718,12 +7610,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>-                                                                                                                                          every</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Travel costs</t>
+          <t>-                                                                                                                                          every for Equity statements 122,764 62,500 (1,116) (80,455) 103,693</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -7732,8 +7624,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>0.007395</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -7745,15 +7639,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I76" s="5" t="n">
+        <v>0.037176</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>-0.06651700000000001</v>
       </c>
     </row>
     <row r="77">
@@ -7764,26 +7654,24 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Loss per share</t>
+          <t>in</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Basic</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>in</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F77" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -7814,43 +7702,605 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>General and administrative (note 5) $</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" s="5" t="n">
+        <v>-0.000172</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>0.015969</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Net Loss and Comprehensive Loss for the Year $</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" s="5" t="n">
+        <v>-0.039942</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Basic and Diluted Loss Per Common Share $ $</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>-                                                                                                                                          every</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>-                                                                                                                                          every for Equity statements 162,706 (39,942) 122,764 62,500 (1,116)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="n">
+        <v>0.103693</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>-0.080455</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>General and administrative fees</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.003459</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>-0.000172</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>0.02655</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.059351</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.01966</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-0.046276</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>-0.082369</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>-0.039942</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Loss and comprehensive per share</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Revenue $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Share-based compensation</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>0.003057</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Travel costs</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>0.007395</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>Loss per share</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Basic</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Loss per share</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
         <is>
           <t>Diluted</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>DilutedEPS</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F78" s="5" t="n">
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
         <v>-1e-08</v>
       </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
         <is>
           <t>-</t>
         </is>
